--- a/VerveStacks_TUR_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_TUR_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TUR_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484A22B6-0E76-47EB-A35C-131BC1DE7B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35AE66E4-CDF5-448A-AD5D-BE0991EFFF26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="11422" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12772" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -750,13 +750,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S3aH2,S4aH2,S2aH2,S1aH2</t>
+    <t>S1aH2,S4aH2,S2aH2,S3aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S2aH1,S2aH3,S1aH1,S4aH3,S3aH3,S4aH1,S3aH1,S1aH3</t>
+    <t>S1aH3,S3aH1,S2aH1,S3aH3,S4aH1,S1aH1,S4aH3,S2aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S2aH1,S2aH3,S1aH1,S4aH3,S3aH3,S4aH1,S3aH1,S1aH3</v>
+        <v>S1aH3,S3aH1,S2aH1,S3aH3,S4aH1,S1aH1,S4aH3,S2aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S3aH2,S4aH2,S2aH2,S1aH2</v>
+        <v>S1aH2,S4aH2,S2aH2,S3aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1464,7 +1464,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41826254-6D05-45D9-8A90-D7688D61482E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76A2E2CC-A681-4B18-83A5-82559731F321}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1544,7 +1544,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC214A1B-EDA6-483F-ADB7-9D956300E743}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E155C2A-A982-4508-BA43-5A727DC29AE4}">
   <dimension ref="B9:O418"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13366,7 +13366,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1ACAB9F-3569-4CA3-9559-467F2838C766}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBB3E042-B7BC-4475-8E4D-A74E695A2A64}">
   <dimension ref="B9:CI86"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -30465,7 +30465,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D815A05E-CB26-4602-8F7E-C7093410C0DD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4C2D5A8-7417-4115-8ADF-B27944F36736}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
